--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_la_araucania.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_la_araucania.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t xml:space="preserve">Categoria</t>
   </si>
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 21:15</t>
+    <t xml:space="preserve">2026-08-07 07:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -60,16 +60,25 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">plot_regional_cobertura_2024_la_araucania.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">Cobertura de residentes</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Region de La Araucanía</t>
+  </si>
+  <si>
     <t xml:space="preserve">Año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024</t>
   </si>
   <si>
     <t xml:space="preserve">region</t>
@@ -606,23 +615,23 @@
         <v>14</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -645,10 +654,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -662,10 +671,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>540817</v>
@@ -679,10 +688,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>558927</v>
@@ -715,10 +724,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -732,10 +741,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>233318</v>
@@ -749,10 +758,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>866426</v>
@@ -785,10 +794,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -802,10 +811,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>44903</v>
@@ -819,10 +828,10 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>67281</v>
@@ -836,10 +845,10 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>75330</v>
@@ -853,10 +862,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>74407</v>
@@ -870,10 +879,10 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>71241</v>
@@ -887,10 +896,10 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>76894</v>
@@ -904,10 +913,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>86247</v>
@@ -921,10 +930,10 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C9" s="2" t="n">
         <v>79547</v>
@@ -938,10 +947,10 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C10" s="2" t="n">
         <v>73734</v>
@@ -955,10 +964,10 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>67276</v>
@@ -972,10 +981,10 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C12" s="2" t="n">
         <v>72681</v>
@@ -989,10 +998,10 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>70392</v>
@@ -1006,10 +1015,10 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C14" s="2" t="n">
         <v>65724</v>
@@ -1023,10 +1032,10 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C15" s="2" t="n">
         <v>54977</v>
@@ -1040,10 +1049,10 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C16" s="2" t="n">
         <v>42752</v>
@@ -1057,10 +1066,10 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C17" s="2" t="n">
         <v>32064</v>
@@ -1074,10 +1083,10 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C18" s="2" t="n">
         <v>44294</v>

--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_la_araucania.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_la_araucania.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-07 07:13</t>
+    <t xml:space="preserve">2026-08-28 11:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_la_araucania.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_la_araucania.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 11:13</t>
+    <t xml:space="preserve">2026-09-01 13:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_la_araucania.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_la_araucania.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-01 13:23</t>
+    <t xml:space="preserve">2026-09-06 17:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_la_araucania.xlsx
+++ b/output/graficos_regionales_cobertura/plot_regional_cobertura_2024_la_araucania.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:19</t>
+    <t xml:space="preserve">2026-09-08 13:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
